--- a/campus-placement/qa/C-4-Non-Hardcoded-Data-Validation.xlsx
+++ b/campus-placement/qa/C-4-Non-Hardcoded-Data-Validation.xlsx
@@ -590,15 +590,11 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="O2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -671,15 +667,11 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="O3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -752,15 +744,11 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="O4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -833,15 +821,11 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="O5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -914,15 +898,11 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="O6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -995,15 +975,11 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="O7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1076,15 +1052,11 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="O8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1157,15 +1129,11 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="O9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1238,15 +1206,11 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="O10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1319,15 +1283,11 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="O11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1400,15 +1360,11 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="O12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1481,15 +1437,11 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr"/>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="O13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1562,15 +1514,11 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="O14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1643,15 +1591,11 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="O15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1724,15 +1668,11 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="O16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1805,15 +1745,11 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="O17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1886,15 +1822,11 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="O18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1967,15 +1899,11 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not Run</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>Automated test execution</t>
-        </is>
-      </c>
+      <c r="O19" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
